--- a/backend/signal_logs/signals_2026-08-08.xlsx
+++ b/backend/signal_logs/signals_2026-08-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1196,12 +1196,635 @@
           <t>NSE:M&amp;M26AUG3500CE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1658</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="K9" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="L9" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="M9" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="U9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26AUG1660CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>249.95</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>250</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7575</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="S10" t="n">
+        <v>34</v>
+      </c>
+      <c r="T10" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="U10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:CROMPTON26AUG250PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I11" t="n">
+        <v>160</v>
+      </c>
+      <c r="J11" t="n">
+        <v>112.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="L11" t="n">
+        <v>227.63</v>
+      </c>
+      <c r="M11" t="n">
+        <v>261.44</v>
+      </c>
+      <c r="N11" t="n">
+        <v>312</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="S11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="U11" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H12" t="n">
+        <v>485</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="K12" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="M12" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3367</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="S12" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="U12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG485CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2265.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2260</v>
+      </c>
+      <c r="I13" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="L13" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="M13" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="N13" t="n">
+        <v>598</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>37</v>
+      </c>
+      <c r="T13" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:BHARATFORG26AUG2260CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>818.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H14" t="n">
+        <v>820</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2109</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="S14" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="U14" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26AUG820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:55:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3502</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I15" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="K15" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="M15" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>680</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="S15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="U15" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:M&amp;M26AUG3500CE</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
